--- a/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}ppc-1:ポリシーまたはPolicyruleのいずれか / Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:scope =プライバシーの場合、患者がいる必要があります / IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:scope =研究の場合、患者がいる必要があります / IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:scope = adrの場合、患者がいる必要があります / IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:scope =治療の場合、患者がいる必要があります / IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}ppc-1:ポリシーまたはPolicyruleのいずれか / Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:scope =プライバシーの場合、患者がいる必要があります / IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:scope =研究の場合、患者がいる必要があります / IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:scope = adrの場合、患者がいる必要があります / IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:scope =治療の場合、患者がいる必要があります / IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -382,7 +382,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Consent.meta.versionId</t>
@@ -669,7 +669,7 @@
     <t>Consent.status</t>
   </si>
   <si>
-    <t>ドラフト|提案|アクティブ|拒否|非アクティブ|エラーに入った / draft | proposed | active | rejected | inactive | entered-in-error</t>
+    <t>ドラフト | 提案 | アクティブ | 拒否 | 非アクティブ | エラー入力 / draft | proposed | active | rejected | inactive | entered-in-error</t>
   </si>
   <si>
     <t>この同意の現在の状態を示します。 / Indicates the current state of this consent.</t>
@@ -1081,13 +1081,13 @@
     <t>Consent.provision.actor.role</t>
   </si>
   <si>
-    <t>俳優がどのように関与しているか / How the actor is involved</t>
+    <t>同意書対象者がどのように関与しているか / How the actor is involved</t>
   </si>
   <si>
     <t>個人が例外で説明されているリソースコンテンツにどのように関与しているか。 / How the individual is involved in the resources content that is described in the exception.</t>
   </si>
   <si>
-    <t>俳優が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
+    <t>同意書対象者が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
@@ -1100,10 +1100,10 @@
 </t>
   </si>
   <si>
-    <t>俳優のためのリソース（またはグループ、役割） / Resource for the actor (or group, by role)</t>
-  </si>
-  <si>
-    <t>俳優を識別するリソース。タイプごとに俳優を特定するには、グループを使用して、共有する一部の財産（「役員を入院する」など）によって一連のアクターを特定します。 / The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+    <t>同意書対象者のためのリソース（またはグループ、役割） / Resource for the actor (or group, by role)</t>
+  </si>
+  <si>
+    <t>同意書対象者を識別するリソース。タイプごとに同意書対象者を特定するには、グループを使用して、共有する一部の財産（「役員を入院する」など）によって一連のアクターを特定します。 / The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
   </si>
   <si>
     <t>Consent.provision.action</t>
@@ -1184,7 +1184,7 @@
     <t>Consent.provision.code</t>
   </si>
   <si>
-    <t>例えばコンテンツ内の泡またはSNOMED-CTコードなど / e.g. LOINC or SNOMED CT code, etc. in the content</t>
+    <t>例えばコンテンツ内のLoincまたはSNOMED-CTコードなど / e.g. LOINC or SNOMED CT code, etc. in the content</t>
   </si>
   <si>
     <t>このコードがインスタンスで見つかった場合、ルールが適用されます。 / If this code is found in an instance, then the rule applies.</t>

--- a/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
@@ -1586,17 +1586,17 @@
   <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.04296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.7890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1605,26 +1605,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="55.12890625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="190.44921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="47.265625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="163.27734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.85546875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.59375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
@@ -446,7 +446,7 @@
     <t>Consent.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -542,7 +542,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>同意リソースの4つの予想される使用。 / The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -733,7 +733,7 @@
     <t>同意声明で見つかった同意のタイプの分類。 / A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -751,7 +751,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -854,7 +854,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>この同意が得られる情報源 / Source from which this consent is taken</t>
@@ -955,7 +955,7 @@
     <t>規制政策の例。 / Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -992,7 +992,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1090,13 +1090,13 @@
     <t>同意書対象者が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>同意措置の詳細なコード。 / Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1178,7 +1178,7 @@
     <t>同意ルールがカバーする情報のクラス（タイプ）。 / The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1196,7 +1196,7 @@
     <t>このコードがインスタンスで見つかった場合、例外が適用されます。 / If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1250,7 +1250,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1596,7 +1596,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.7890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-consent.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
